--- a/output/pdf_financials_xlsx/OGN.xlsx
+++ b/output/pdf_financials_xlsx/OGN.xlsx
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.030636</v>
+        <v>-0.030636</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.119164</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.030636</v>
+        <v>-0.030636</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.119164</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.030636</v>
+        <v>-0.030636</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.119164</v>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.030636</v>
+        <v>-0.030636</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.119164</v>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.030636</v>
+        <v>-0.030636</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.119164</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -6176,7 +6176,7 @@
         <v>3.297743</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0.589098</v>
+        <v>-43.27876</v>
       </c>
     </row>
     <row r="93">
@@ -10926,7 +10926,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -71362,10 +71366,10 @@
         </is>
       </c>
       <c r="E633" s="5" t="n">
-        <v>0.030636</v>
+        <v>-0.030636</v>
       </c>
       <c r="F633" s="5" t="n">
-        <v>0.119164</v>
+        <v>-0.119164</v>
       </c>
       <c r="G633" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OGN.xlsx
+++ b/output/pdf_financials_xlsx/OGN.xlsx
@@ -1063,25 +1063,25 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.109643</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.215619</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.100136</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.089889</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.256557</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.578475</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.45863</v>
       </c>
     </row>
     <row r="13">
@@ -2007,25 +2007,25 @@
         <v>-2.542081</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.983127</v>
+        <v>-2.09277</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.232856</v>
+        <v>-3.448475</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.696524</v>
+        <v>-2.79666</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.7114819999999999</v>
+        <v>0.621593</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>4.168208</v>
+        <v>3.911651</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.925582</v>
+        <v>0.347107</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.057857</v>
+        <v>1.599227</v>
       </c>
     </row>
     <row r="28">
@@ -2123,25 +2123,25 @@
         <v>-2.525232</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.931282</v>
+        <v>-2.040925</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.053952</v>
+        <v>-3.269571</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.509525</v>
+        <v>-2.609661</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.841027</v>
+        <v>0.751138</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>4.259041</v>
+        <v>4.002484</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.006506</v>
+        <v>0.428031</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.137905</v>
+        <v>1.679275</v>
       </c>
     </row>
     <row r="30">
@@ -2187,25 +2187,25 @@
         <v>-1066.650897171628</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-79.38322771685495</v>
+        <v>-83.88998293776993</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-551.4818372904372</v>
+        <v>-590.4182587779809</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-151.647133115186</v>
+        <v>-157.6982134278437</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>95.44998513252482</v>
+        <v>85.24828683558843</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>226.6213995798579</v>
+        <v>212.9701324490626</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>70.89952755062436</v>
+        <v>30.15103305595922</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>70.32140414862093</v>
+        <v>55.23583880091745</v>
       </c>
     </row>
     <row r="31">
@@ -20483,7 +20483,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -56733,7 +56733,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -59250,7 +59250,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -59953,7 +59953,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -63454,7 +63454,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
